--- a/src/test/resources/testdata/TestData.xlsx
+++ b/src/test/resources/testdata/TestData.xlsx
@@ -1,18 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10306"/>
   <workbookPr/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F35F1D19-7CA1-6A4A-97E8-4C155CABA9E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="LoginData" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="EditorData" sheetId="2" r:id="rId6"/>
+    <sheet name="LoginData" sheetId="1" r:id="rId1"/>
+    <sheet name="ArrayData" sheetId="3" r:id="rId2"/>
+    <sheet name="EditorData" sheetId="2" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="32">
   <si>
     <t>TestCaseName</t>
   </si>
@@ -72,20 +90,57 @@
   </si>
   <si>
     <t>print Failure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TestCaseName </t>
+  </si>
+  <si>
+    <t>ExpectedResults</t>
+  </si>
+  <si>
+    <t>TC-A01</t>
+  </si>
+  <si>
+    <t>TC-A02</t>
+  </si>
+  <si>
+    <t>TC-A03</t>
+  </si>
+  <si>
+    <t>TC-A04</t>
+  </si>
+  <si>
+    <t>print('NumpyNinja')</t>
+  </si>
+  <si>
+    <t>print(3+4)</t>
+  </si>
+  <si>
+    <t>print('4+1')</t>
+  </si>
+  <si>
+    <t>print(9-6)</t>
+  </si>
+  <si>
+    <t>NumpyNinja</t>
+  </si>
+  <si>
+    <t>Error</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -96,44 +151,43 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -323,22 +377,25 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultColWidth="12.67578125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="18.13"/>
-    <col customWidth="1" min="2" max="3" width="20.13"/>
-    <col customWidth="1" min="4" max="4" width="24.63"/>
+    <col min="1" max="1" width="18.0703125" customWidth="1"/>
+    <col min="2" max="3" width="20.08984375" customWidth="1"/>
+    <col min="4" max="4" width="24.67578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -352,7 +409,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:4" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -366,7 +423,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:4" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -380,7 +437,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:4" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
@@ -394,7 +451,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:4" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
@@ -409,23 +466,95 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9C034C9-96FE-CD43-97A2-BCB590DB4D8D}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="14.5625" customWidth="1"/>
+    <col min="2" max="2" width="16.98828125" customWidth="1"/>
+    <col min="3" max="3" width="21.57421875" customWidth="1"/>
+    <col min="4" max="4" width="16.046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultColWidth="12.67578125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="17.0"/>
-    <col customWidth="1" min="2" max="2" width="18.5"/>
-    <col customWidth="1" min="3" max="3" width="20.63"/>
+    <col min="1" max="1" width="16.98828125" customWidth="1"/>
+    <col min="2" max="2" width="18.47265625" customWidth="1"/>
+    <col min="3" max="3" width="20.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -436,7 +565,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>16</v>
       </c>
@@ -447,7 +576,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:3" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>18</v>
       </c>
@@ -459,6 +588,6 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/src/test/resources/testdata/TestData.xlsx
+++ b/src/test/resources/testdata/TestData.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10306"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F35F1D19-7CA1-6A4A-97E8-4C155CABA9E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{705E0842-7C65-084F-9052-38886462DB48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="34">
   <si>
     <t>TestCaseName</t>
   </si>
@@ -116,9 +116,6 @@
     <t>print(3+4)</t>
   </si>
   <si>
-    <t>print('4+1')</t>
-  </si>
-  <si>
     <t>print(9-6)</t>
   </si>
   <si>
@@ -126,6 +123,9 @@
   </si>
   <si>
     <t>Error</t>
+  </si>
+  <si>
+    <t>print('4+1)</t>
   </si>
 </sst>
 </file>
@@ -500,7 +500,7 @@
         <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.15">
@@ -519,10 +519,10 @@
         <v>24</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.15">
@@ -530,7 +530,7 @@
         <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C5">
         <v>3</v>

--- a/src/test/resources/testdata/TestData.xlsx
+++ b/src/test/resources/testdata/TestData.xlsx
@@ -3,15 +3,19 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10306"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{705E0842-7C65-084F-9052-38886462DB48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{28104228-5E3D-794F-9207-697D571F3499}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LoginData" sheetId="1" r:id="rId1"/>
     <sheet name="ArrayData" sheetId="3" r:id="rId2"/>
-    <sheet name="EditorData" sheetId="2" r:id="rId3"/>
+    <sheet name="ArrayTry" sheetId="5" r:id="rId3"/>
+    <sheet name="EditorData" sheetId="2" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">ArrayTry!$A$1:$D$3</definedName>
+  </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -30,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="41">
   <si>
     <t>TestCaseName</t>
   </si>
@@ -98,18 +102,6 @@
     <t>ExpectedResults</t>
   </si>
   <si>
-    <t>TC-A01</t>
-  </si>
-  <si>
-    <t>TC-A02</t>
-  </si>
-  <si>
-    <t>TC-A03</t>
-  </si>
-  <si>
-    <t>TC-A04</t>
-  </si>
-  <si>
     <t>print('NumpyNinja')</t>
   </si>
   <si>
@@ -126,13 +118,52 @@
   </si>
   <si>
     <t>print('4+1)</t>
+  </si>
+  <si>
+    <t>PrintString</t>
+  </si>
+  <si>
+    <t>Addition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subtraction </t>
+  </si>
+  <si>
+    <t>Questions</t>
+  </si>
+  <si>
+    <t>Results</t>
+  </si>
+  <si>
+    <t>Search array</t>
+  </si>
+  <si>
+    <t>MaxConsecutiveOnes</t>
+  </si>
+  <si>
+    <t>Search the array</t>
+  </si>
+  <si>
+    <t>Max Consecutive Ones</t>
+  </si>
+  <si>
+    <t>nums = [1,1,0,1,1,1]\ncount = 0\nmax_count = 0\nfor i in nums :\n if i == 1:\n count += 1\n max_count = max(max_count,count)\n else:\n count = 0\nprint(max_count)</t>
+  </si>
+  <si>
+    <t>N=[3,7,9,44];print(3 in N)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FindEven </t>
+  </si>
+  <si>
+    <t>SyntaxError</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -144,6 +175,12 @@
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="13.5"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="-Webkit-Standard"/>
+      <family val="18"/>
     </font>
   </fonts>
   <fills count="2">
@@ -166,9 +203,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -475,7 +518,7 @@
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="14.5625" customWidth="1"/>
+    <col min="1" max="1" width="17.80078125" customWidth="1"/>
     <col min="2" max="2" width="16.98828125" customWidth="1"/>
     <col min="3" max="3" width="21.57421875" customWidth="1"/>
     <col min="4" max="4" width="16.046875" customWidth="1"/>
@@ -494,21 +537,21 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" t="s">
         <v>22</v>
       </c>
-      <c r="B2" t="s">
-        <v>26</v>
-      </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" t="s">
         <v>23</v>
-      </c>
-      <c r="B3" t="s">
-        <v>27</v>
       </c>
       <c r="C3">
         <v>7</v>
@@ -516,21 +559,21 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C5">
         <v>3</v>
@@ -542,6 +585,72 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8DA781C-8D6E-174F-A4BE-34ED56B21D9F}">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="34.51953125" customWidth="1"/>
+    <col min="2" max="2" width="15.77734375" customWidth="1"/>
+    <col min="3" max="3" width="34.51953125" customWidth="1"/>
+    <col min="4" max="4" width="16.31640625" style="2" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="139.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="165" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="3"/>
+    </row>
+    <row r="5" spans="1:4" ht="121.5" customHeight="1" x14ac:dyDescent="0.15"/>
+  </sheetData>
+  <autoFilter ref="A1:D3" xr:uid="{B8DA781C-8D6E-174F-A4BE-34ED56B21D9F}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>

--- a/src/test/resources/testdata/TestData.xlsx
+++ b/src/test/resources/testdata/TestData.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10306"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{28104228-5E3D-794F-9207-697D571F3499}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{40CFC344-37CF-5540-A8E2-4BB73FE8FF6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LoginData" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="42">
   <si>
     <t>TestCaseName</t>
   </si>
@@ -108,9 +108,6 @@
     <t>print(3+4)</t>
   </si>
   <si>
-    <t>print(9-6)</t>
-  </si>
-  <si>
     <t>NumpyNinja</t>
   </si>
   <si>
@@ -126,9 +123,6 @@
     <t>Addition</t>
   </si>
   <si>
-    <t xml:space="preserve">Subtraction </t>
-  </si>
-  <si>
     <t>Questions</t>
   </si>
   <si>
@@ -157,6 +151,9 @@
   </si>
   <si>
     <t>SyntaxError</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -537,18 +534,18 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
@@ -559,24 +556,18 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5">
-        <v>3</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -600,24 +591,24 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C1" t="s">
         <v>14</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
         <v>33</v>
       </c>
-      <c r="B2" t="s">
-        <v>35</v>
-      </c>
       <c r="C2" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D2" s="2" t="b">
         <v>1</v>
@@ -625,21 +616,21 @@
     </row>
     <row r="3" spans="1:4" ht="139.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s">
         <v>34</v>
       </c>
-      <c r="B3" t="s">
-        <v>36</v>
-      </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="165" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C4" s="3"/>
     </row>
